--- a/data/trans_orig/P13A_1_2023-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P13A_1_2023-Edad-trans_orig.xlsx
@@ -760,27 +760,27 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>12765</t>
+          <t>16059</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>5707</t>
+          <t>8436</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>16480</t>
+          <t>19847</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>77,46%</t>
+          <t>80,92%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>34,63%</t>
+          <t>42,51%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -795,27 +795,27 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>12765</t>
+          <t>16059</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>5707</t>
+          <t>8436</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>16480</t>
+          <t>19847</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>77,46%</t>
+          <t>80,92%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>34,63%</t>
+          <t>42,51%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -873,7 +873,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>3715</t>
+          <t>3788</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -883,12 +883,12 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>10773</t>
+          <t>11359</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>22,54%</t>
+          <t>19,08%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>65,37%</t>
+          <t>57,23%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,7 +908,7 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>3715</t>
+          <t>3788</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
@@ -918,12 +918,12 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>10773</t>
+          <t>11359</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>22,54%</t>
+          <t>19,08%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
@@ -933,7 +933,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>65,37%</t>
+          <t>57,23%</t>
         </is>
       </c>
     </row>
@@ -986,17 +986,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>16480</t>
+          <t>19847</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>16480</t>
+          <t>19847</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>16480</t>
+          <t>19847</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>16480</t>
+          <t>19847</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>16480</t>
+          <t>19847</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>16480</t>
+          <t>19847</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1068,7 +1068,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>4434</t>
+          <t>5404</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -1103,27 +1103,27 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>7713</t>
+          <t>8924</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3304</t>
+          <t>5529</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>8819</t>
+          <t>10003</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>87,46%</t>
+          <t>89,22%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>37,46%</t>
+          <t>55,28%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1138,27 +1138,27 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>12147</t>
+          <t>14327</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>8336</t>
+          <t>9934</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>13253</t>
+          <t>15406</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>91,66%</t>
+          <t>93,0%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>62,9%</t>
+          <t>64,48%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -1216,7 +1216,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>1106</t>
+          <t>1079</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -1226,12 +1226,12 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>5515</t>
+          <t>4474</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>12,54%</t>
+          <t>10,78%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
@@ -1241,7 +1241,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>62,54%</t>
+          <t>44,72%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,7 +1251,7 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>1106</t>
+          <t>1079</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
@@ -1261,12 +1261,12 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4917</t>
+          <t>5472</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>8,34%</t>
+          <t>7,0%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
@@ -1276,7 +1276,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>37,1%</t>
+          <t>35,52%</t>
         </is>
       </c>
     </row>
@@ -1294,17 +1294,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4434</t>
+          <t>5404</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4434</t>
+          <t>5404</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4434</t>
+          <t>5404</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1329,17 +1329,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>8819</t>
+          <t>10003</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>8819</t>
+          <t>10003</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>8819</t>
+          <t>10003</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>13253</t>
+          <t>15406</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>13253</t>
+          <t>15406</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>13253</t>
+          <t>15406</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1411,7 +1411,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>6979</t>
+          <t>7122</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1446,27 +1446,27 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>17497</t>
+          <t>18743</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>16562</t>
+          <t>15233</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>17660</t>
+          <t>19652</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>99,08%</t>
+          <t>95,38%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>93,78%</t>
+          <t>77,51%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1481,27 +1481,27 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>24476</t>
+          <t>25865</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>23849</t>
+          <t>22914</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>24639</t>
+          <t>26774</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>99,34%</t>
+          <t>96,61%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>96,79%</t>
+          <t>85,58%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -1559,7 +1559,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>163</t>
+          <t>909</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -1569,12 +1569,12 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1098</t>
+          <t>4419</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
@@ -1584,7 +1584,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>22,49%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,7 +1594,7 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>163</t>
+          <t>909</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
@@ -1604,12 +1604,12 @@
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>790</t>
+          <t>3860</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>14,42%</t>
         </is>
       </c>
     </row>
@@ -1637,17 +1637,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>6979</t>
+          <t>7122</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>6979</t>
+          <t>7122</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>6979</t>
+          <t>7122</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1672,17 +1672,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>17660</t>
+          <t>19652</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>17660</t>
+          <t>19652</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>17660</t>
+          <t>19652</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>24639</t>
+          <t>26774</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>24639</t>
+          <t>26774</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>24639</t>
+          <t>26774</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1754,7 +1754,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>7234</t>
+          <t>7391</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1789,27 +1789,27 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>41671</t>
+          <t>41032</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>37723</t>
+          <t>37362</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>43025</t>
+          <t>42479</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>96,85%</t>
+          <t>96,59%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>87,68%</t>
+          <t>87,95%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1824,27 +1824,27 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>48905</t>
+          <t>48423</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>45712</t>
+          <t>44798</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>50259</t>
+          <t>49870</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>97,31%</t>
+          <t>97,1%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>90,95%</t>
+          <t>89,83%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -1902,7 +1902,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>1354</t>
+          <t>1447</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
@@ -1912,12 +1912,12 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>5302</t>
+          <t>5117</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
@@ -1927,7 +1927,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>12,32%</t>
+          <t>12,05%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,7 +1937,7 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1354</t>
+          <t>1447</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
@@ -1947,12 +1947,12 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>4547</t>
+          <t>5072</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
@@ -1962,7 +1962,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>9,05%</t>
+          <t>10,17%</t>
         </is>
       </c>
     </row>
@@ -1980,17 +1980,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>7234</t>
+          <t>7391</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>7234</t>
+          <t>7391</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>7234</t>
+          <t>7391</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2015,17 +2015,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>43025</t>
+          <t>42479</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>43025</t>
+          <t>42479</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>43025</t>
+          <t>42479</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>50259</t>
+          <t>49870</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>50259</t>
+          <t>49870</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>50259</t>
+          <t>49870</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2097,7 +2097,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>10183</t>
+          <t>11016</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -2132,27 +2132,27 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>29562</t>
+          <t>32439</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>27586</t>
+          <t>30476</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>30418</t>
+          <t>33328</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>97,19%</t>
+          <t>97,33%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>90,69%</t>
+          <t>91,44%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2167,27 +2167,27 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>39745</t>
+          <t>43455</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>37845</t>
+          <t>40992</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>40601</t>
+          <t>44344</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>97,89%</t>
+          <t>98,0%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>93,21%</t>
+          <t>92,44%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -2245,7 +2245,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>856</t>
+          <t>889</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
@@ -2255,12 +2255,12 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2832</t>
+          <t>2852</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
@@ -2270,7 +2270,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>9,31%</t>
+          <t>8,56%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,7 +2280,7 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>856</t>
+          <t>889</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
@@ -2290,12 +2290,12 @@
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>2756</t>
+          <t>3352</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
@@ -2305,7 +2305,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>7,56%</t>
         </is>
       </c>
     </row>
@@ -2323,17 +2323,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>10183</t>
+          <t>11016</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>10183</t>
+          <t>11016</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>10183</t>
+          <t>11016</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2358,17 +2358,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>30418</t>
+          <t>33328</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>30418</t>
+          <t>33328</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>30418</t>
+          <t>33328</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>40601</t>
+          <t>44344</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>40601</t>
+          <t>44344</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>40601</t>
+          <t>44344</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2440,7 +2440,7 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>3946</t>
+          <t>4033</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -2475,7 +2475,7 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>16407</t>
+          <t>17681</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
@@ -2510,7 +2510,7 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>20353</t>
+          <t>21714</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
@@ -2666,17 +2666,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>3946</t>
+          <t>4033</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>3946</t>
+          <t>4033</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>3946</t>
+          <t>4033</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2701,17 +2701,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>16407</t>
+          <t>17681</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>16407</t>
+          <t>17681</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>16407</t>
+          <t>17681</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2736,17 +2736,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>20353</t>
+          <t>21714</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>20353</t>
+          <t>21714</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>20353</t>
+          <t>21714</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2783,7 +2783,7 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>4618</t>
+          <t>4942</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -2818,22 +2818,22 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>17878</t>
+          <t>20203</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>15626</t>
+          <t>17560</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>19024</t>
+          <t>21377</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>93,97%</t>
+          <t>94,51%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
@@ -2853,27 +2853,27 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>22496</t>
+          <t>25145</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>20236</t>
+          <t>22780</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>23642</t>
+          <t>26319</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>95,15%</t>
+          <t>95,54%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>85,6%</t>
+          <t>86,55%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>1146</t>
+          <t>1174</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
@@ -2941,12 +2941,12 @@
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3398</t>
+          <t>3817</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
@@ -2966,7 +2966,7 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1146</t>
+          <t>1174</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>3406</t>
+          <t>3539</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
@@ -2991,7 +2991,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>14,4%</t>
+          <t>13,45%</t>
         </is>
       </c>
     </row>
@@ -3009,17 +3009,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>4618</t>
+          <t>4942</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>4618</t>
+          <t>4942</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>4618</t>
+          <t>4942</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3044,17 +3044,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>19024</t>
+          <t>21377</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>19024</t>
+          <t>21377</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>19024</t>
+          <t>21377</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3079,17 +3079,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>23642</t>
+          <t>26319</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>23642</t>
+          <t>26319</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>23642</t>
+          <t>26319</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3126,7 +3126,7 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>37393</t>
+          <t>39908</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -3161,32 +3161,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>143494</t>
+          <t>155080</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>134306</t>
+          <t>146218</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>147895</t>
+          <t>159931</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>94,51%</t>
+          <t>94,35%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>88,46%</t>
+          <t>88,96%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>97,41%</t>
+          <t>97,3%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3196,32 +3196,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>180887</t>
+          <t>194989</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>171861</t>
+          <t>185120</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>185399</t>
+          <t>199435</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>95,59%</t>
+          <t>95,45%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>90,82%</t>
+          <t>90,62%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>97,98%</t>
+          <t>97,63%</t>
         </is>
       </c>
     </row>
@@ -3274,32 +3274,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>8340</t>
+          <t>9286</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3939</t>
+          <t>4435</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>17528</t>
+          <t>18148</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>11,54%</t>
+          <t>11,04%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3309,32 +3309,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>8340</t>
+          <t>9286</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>3828</t>
+          <t>4840</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>17366</t>
+          <t>19155</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>9,18%</t>
+          <t>9,38%</t>
         </is>
       </c>
     </row>
@@ -3352,17 +3352,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>37393</t>
+          <t>39908</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>37393</t>
+          <t>39908</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>37393</t>
+          <t>39908</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3387,17 +3387,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>151834</t>
+          <t>164366</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>151834</t>
+          <t>164366</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>151834</t>
+          <t>164366</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3422,17 +3422,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>189227</t>
+          <t>204275</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>189227</t>
+          <t>204275</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>189227</t>
+          <t>204275</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
